--- a/data/trans_orig/Q04C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda</t>
+          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 22,27</t>
+          <t>17,86; 22,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,42; 24,7</t>
+          <t>21,48; 24,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,24; 23,09</t>
+          <t>20,27; 23,01</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,8; 20,45</t>
+          <t>16,91; 20,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,51; 24,71</t>
+          <t>21,56; 24,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,53; 22,07</t>
+          <t>19,48; 22,14</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,51; 23,84</t>
+          <t>20,41; 24,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,01; 24,93</t>
+          <t>20,94; 24,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,3; 23,92</t>
+          <t>21,24; 23,9</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,53; 24,44</t>
+          <t>18,89; 24,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 22,91</t>
+          <t>18,31; 22,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,22; 22,96</t>
+          <t>19,14; 22,88</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 21,34</t>
+          <t>17,56; 21,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,69; 23,04</t>
+          <t>19,76; 22,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,21; 21,7</t>
+          <t>19,24; 21,55</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,88; 22,9</t>
+          <t>18,98; 23,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,67; 25,33</t>
+          <t>21,57; 25,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,84; 23,68</t>
+          <t>20,87; 23,61</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,38; 21,72</t>
+          <t>18,52; 21,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,66; 24,72</t>
+          <t>21,68; 24,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,9; 23,86</t>
+          <t>20,82; 23,88</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,15; 21,64</t>
+          <t>19,1; 21,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 22,07</t>
+          <t>19,66; 21,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,73; 21,49</t>
+          <t>19,72; 21,57</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,58; 21,04</t>
+          <t>19,57; 20,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,28</t>
+          <t>21,77; 23,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,98; 22,02</t>
+          <t>20,95; 22,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Provincia-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20,05</t>
+          <t>18,67</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23,07</t>
+          <t>21,38</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,59</t>
+          <t>20,08</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 22,41</t>
+          <t>16,7; 20,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,48; 24,79</t>
+          <t>19,51; 23,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,27; 23,01</t>
+          <t>18,74; 21,42</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18,64</t>
+          <t>18,52</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,12</t>
+          <t>22,81</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,78</t>
+          <t>20,62</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,91; 20,59</t>
+          <t>16,71; 20,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,56; 24,96</t>
+          <t>21,23; 24,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,48; 22,14</t>
+          <t>19,28; 21,91</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>21,49</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,84</t>
+          <t>22,44</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,51</t>
+          <t>21,95</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,41; 24,28</t>
+          <t>19,81; 23,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 24,81</t>
+          <t>20,68; 24,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,24; 23,9</t>
+          <t>20,69; 23,27</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21,55</t>
+          <t>20,39</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>21,01</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,09</t>
+          <t>20,72</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 24,71</t>
+          <t>17,55; 23,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 22,82</t>
+          <t>19,17; 23,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,14; 22,88</t>
+          <t>19,13; 22,37</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,25</t>
+          <t>18,47</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21,28</t>
+          <t>20,75</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>19,73</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,56; 21,1</t>
+          <t>16,7; 20,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,76; 22,93</t>
+          <t>19,1; 22,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,24; 21,55</t>
+          <t>18,58; 21,03</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>21,03</t>
+          <t>20,63</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23,49</t>
+          <t>23,09</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22,26</t>
+          <t>21,89</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,98; 23,09</t>
+          <t>18,57; 22,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,57; 25,37</t>
+          <t>21,23; 24,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,87; 23,61</t>
+          <t>20,59; 23,27</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>19,14</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,45</t>
+          <t>21,08</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,26</t>
+          <t>20,17</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,52; 21,93</t>
+          <t>17,35; 20,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,68; 24,88</t>
+          <t>19,66; 22,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,82; 23,88</t>
+          <t>19,15; 21,45</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20,31</t>
+          <t>19,64</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20,88</t>
+          <t>20,73</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20,59</t>
+          <t>20,18</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,1; 21,69</t>
+          <t>18,39; 20,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,66; 21,96</t>
+          <t>19,5; 21,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,72; 21,57</t>
+          <t>19,32; 21,01</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>19,57</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>21,55</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21,45</t>
+          <t>20,58</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,57; 20,98</t>
+          <t>18,91; 20,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,77; 23,3</t>
+          <t>20,94; 22,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,95; 22,1</t>
+          <t>20,15; 21,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
+          <t>Tiempo medio en años que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
